--- a/Post-processing.xlsx
+++ b/Post-processing.xlsx
@@ -469,6 +469,11 @@
       <c r="A2" s="1" t="n">
         <v>0.25</v>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">

--- a/Post-processing.xlsx
+++ b/Post-processing.xlsx
@@ -1,33 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\Code\Thesis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC19239-C263-4AF9-8584-7DF621BED85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UV Curing Stations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UV Curing Stations" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Alfred</t>
+  </si>
+  <si>
+    <t>Cassian</t>
+  </si>
+  <si>
+    <t>Bardock</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,88 +89,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -415,255 +399,232 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
         <v>0.25</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>0.29166666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
         <v>0.375</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>0.4583333333333333</v>
-      </c>
-      <c r="E7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>0.5416666666666666</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
         <v>0.625</v>
       </c>
-      <c r="C11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
         <v>0.75</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
         <v>0.875</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n"/>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="1"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="1"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="1"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="1"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="1"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="1"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="1"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="1"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="1"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
